--- a/MaHH.xlsx
+++ b/MaHH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C7B229-A3B6-4A2B-8842-752AC25B10B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F639B7A-EB94-415B-A2BC-38798CE2BDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E1154C90-8187-4C9D-8DDB-7618463980C9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1154C90-8187-4C9D-8DDB-7618463980C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="328">
   <si>
     <t>Đvt</t>
   </si>
@@ -1011,6 +1011,12 @@
   </si>
   <si>
     <t>Xăng dầu</t>
+  </si>
+  <si>
+    <t>Xăng E10 RON95 Mức 3</t>
+  </si>
+  <si>
+    <t>HH051</t>
   </si>
 </sst>
 </file>
@@ -1562,7 +1568,7 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -1580,11 +1586,8 @@
       <alignment vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1632,57 +1635,7 @@
     <cellStyle name="Total" xfId="40" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="41" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2091,7 +2044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9639D367-352F-44BE-8505-63CC30B1FB0F}">
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D162"/>
   <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="63.7109375" bestFit="1" customWidth="1"/>
@@ -2122,7 +2075,7 @@
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2136,7 +2089,7 @@
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2150,7 +2103,7 @@
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2164,7 +2117,7 @@
       <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2178,7 +2131,7 @@
       <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2192,7 +2145,7 @@
       <c r="C7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2206,7 +2159,7 @@
       <c r="C8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2220,7 +2173,7 @@
       <c r="C9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2234,7 +2187,7 @@
       <c r="C10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2248,7 +2201,7 @@
       <c r="C11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2262,7 +2215,7 @@
       <c r="C12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2276,7 +2229,7 @@
       <c r="C13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2290,7 +2243,7 @@
       <c r="C14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2304,7 +2257,7 @@
       <c r="C15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2318,7 +2271,7 @@
       <c r="C16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2332,7 +2285,7 @@
       <c r="C17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2346,7 +2299,7 @@
       <c r="C18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2360,7 +2313,7 @@
       <c r="C19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2374,7 +2327,7 @@
       <c r="C20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2388,7 +2341,7 @@
       <c r="C21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2402,7 +2355,7 @@
       <c r="C22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2416,7 +2369,7 @@
       <c r="C23" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2430,7 +2383,7 @@
       <c r="C24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2444,7 +2397,7 @@
       <c r="C25" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2458,7 +2411,7 @@
       <c r="C26" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2472,7 +2425,7 @@
       <c r="C27" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2486,7 +2439,7 @@
       <c r="C28" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2500,7 +2453,7 @@
       <c r="C29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2514,7 +2467,7 @@
       <c r="C30" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2528,7 +2481,7 @@
       <c r="C31" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2542,7 +2495,7 @@
       <c r="C32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2556,7 +2509,7 @@
       <c r="C33" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2570,7 +2523,7 @@
       <c r="C34" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2584,7 +2537,7 @@
       <c r="C35" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2598,7 +2551,7 @@
       <c r="C36" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2612,7 +2565,7 @@
       <c r="C37" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2626,7 +2579,7 @@
       <c r="C38" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2640,7 +2593,7 @@
       <c r="C39" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2654,7 +2607,7 @@
       <c r="C40" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2668,7 +2621,7 @@
       <c r="C41" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2682,7 +2635,7 @@
       <c r="C42" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2696,7 +2649,7 @@
       <c r="C43" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2710,7 +2663,7 @@
       <c r="C44" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2724,7 +2677,7 @@
       <c r="C45" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2738,7 +2691,7 @@
       <c r="C46" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2752,7 +2705,7 @@
       <c r="C47" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2766,7 +2719,7 @@
       <c r="C48" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2780,7 +2733,7 @@
       <c r="C49" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2794,7 +2747,7 @@
       <c r="C50" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2808,7 +2761,7 @@
       <c r="C51" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2822,7 +2775,7 @@
       <c r="C52" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2836,7 +2789,7 @@
       <c r="C53" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2850,7 +2803,7 @@
       <c r="C54" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2864,7 +2817,7 @@
       <c r="C55" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2878,7 +2831,7 @@
       <c r="C56" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2892,7 +2845,7 @@
       <c r="C57" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2906,7 +2859,7 @@
       <c r="C58" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2920,7 +2873,7 @@
       <c r="C59" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2934,7 +2887,7 @@
       <c r="C60" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D60" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2948,7 +2901,7 @@
       <c r="C61" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D61" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2962,7 +2915,7 @@
       <c r="C62" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="D62" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2976,7 +2929,7 @@
       <c r="C63" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D63" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2990,7 +2943,7 @@
       <c r="C64" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D64" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3004,7 +2957,7 @@
       <c r="C65" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3018,7 +2971,7 @@
       <c r="C66" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D66" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3032,7 +2985,7 @@
       <c r="C67" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D67" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3046,7 +2999,7 @@
       <c r="C68" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3060,7 +3013,7 @@
       <c r="C69" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3074,7 +3027,7 @@
       <c r="C70" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3088,7 +3041,7 @@
       <c r="C71" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D71" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3102,7 +3055,7 @@
       <c r="C72" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D72" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3116,7 +3069,7 @@
       <c r="C73" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="D73" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3130,7 +3083,7 @@
       <c r="C74" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D74" s="6" t="s">
+      <c r="D74" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3144,7 +3097,7 @@
       <c r="C75" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="D75" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3158,7 +3111,7 @@
       <c r="C76" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3172,7 +3125,7 @@
       <c r="C77" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="D77" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3186,7 +3139,7 @@
       <c r="C78" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="D78" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3200,7 +3153,7 @@
       <c r="C79" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="D79" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3214,7 +3167,7 @@
       <c r="C80" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D80" s="6" t="s">
+      <c r="D80" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3228,7 +3181,7 @@
       <c r="C81" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="D81" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3242,7 +3195,7 @@
       <c r="C82" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="D82" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3256,7 +3209,7 @@
       <c r="C83" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="D83" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3270,7 +3223,7 @@
       <c r="C84" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="D84" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3284,7 +3237,7 @@
       <c r="C85" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="D85" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3298,7 +3251,7 @@
       <c r="C86" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D86" s="6" t="s">
+      <c r="D86" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3312,7 +3265,7 @@
       <c r="C87" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D87" s="6" t="s">
+      <c r="D87" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3326,7 +3279,7 @@
       <c r="C88" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D88" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3340,7 +3293,7 @@
       <c r="C89" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="D89" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3354,7 +3307,7 @@
       <c r="C90" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D90" s="6" t="s">
+      <c r="D90" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3368,7 +3321,7 @@
       <c r="C91" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D91" s="6" t="s">
+      <c r="D91" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3382,7 +3335,7 @@
       <c r="C92" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D92" s="6" t="s">
+      <c r="D92" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3396,7 +3349,7 @@
       <c r="C93" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="D93" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3410,7 +3363,7 @@
       <c r="C94" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="D94" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3424,7 +3377,7 @@
       <c r="C95" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="D95" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3438,7 +3391,7 @@
       <c r="C96" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D96" s="6" t="s">
+      <c r="D96" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3452,7 +3405,7 @@
       <c r="C97" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="D97" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3466,7 +3419,7 @@
       <c r="C98" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D98" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3480,7 +3433,7 @@
       <c r="C99" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="D99" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3494,7 +3447,7 @@
       <c r="C100" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="D100" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3508,7 +3461,7 @@
       <c r="C101" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="D101" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3522,7 +3475,7 @@
       <c r="C102" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D102" s="6" t="s">
+      <c r="D102" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3536,7 +3489,7 @@
       <c r="C103" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="D103" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3550,7 +3503,7 @@
       <c r="C104" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D104" s="6" t="s">
+      <c r="D104" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3564,7 +3517,7 @@
       <c r="C105" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="D105" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3578,7 +3531,7 @@
       <c r="C106" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="D106" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3592,7 +3545,7 @@
       <c r="C107" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D107" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3606,7 +3559,7 @@
       <c r="C108" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D108" s="6" t="s">
+      <c r="D108" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3620,7 +3573,7 @@
       <c r="C109" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D109" s="6" t="s">
+      <c r="D109" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3634,7 +3587,7 @@
       <c r="C110" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D110" s="6" t="s">
+      <c r="D110" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3648,7 +3601,7 @@
       <c r="C111" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D111" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3662,7 +3615,7 @@
       <c r="C112" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D112" s="6" t="s">
+      <c r="D112" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3676,7 +3629,7 @@
       <c r="C113" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D113" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3690,7 +3643,7 @@
       <c r="C114" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D114" s="6" t="s">
+      <c r="D114" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3704,7 +3657,7 @@
       <c r="C115" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D115" s="6" t="s">
+      <c r="D115" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3718,7 +3671,7 @@
       <c r="C116" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D116" s="6" t="s">
+      <c r="D116" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3732,7 +3685,7 @@
       <c r="C117" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D117" s="6" t="s">
+      <c r="D117" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3746,7 +3699,7 @@
       <c r="C118" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D118" s="6" t="s">
+      <c r="D118" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3760,7 +3713,7 @@
       <c r="C119" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D119" s="6" t="s">
+      <c r="D119" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3774,7 +3727,7 @@
       <c r="C120" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D120" s="6" t="s">
+      <c r="D120" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3788,7 +3741,7 @@
       <c r="C121" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D121" s="6" t="s">
+      <c r="D121" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3802,7 +3755,7 @@
       <c r="C122" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D122" s="6" t="s">
+      <c r="D122" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3816,7 +3769,7 @@
       <c r="C123" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D123" s="6" t="s">
+      <c r="D123" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3830,7 +3783,7 @@
       <c r="C124" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D124" s="6" t="s">
+      <c r="D124" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3844,7 +3797,7 @@
       <c r="C125" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D125" s="6" t="s">
+      <c r="D125" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3858,7 +3811,7 @@
       <c r="C126" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D126" s="6" t="s">
+      <c r="D126" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3872,7 +3825,7 @@
       <c r="C127" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D127" s="6" t="s">
+      <c r="D127" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3886,7 +3839,7 @@
       <c r="C128" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D128" s="6" t="s">
+      <c r="D128" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3900,7 +3853,7 @@
       <c r="C129" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D129" s="6" t="s">
+      <c r="D129" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3914,7 +3867,7 @@
       <c r="C130" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D130" s="6" t="s">
+      <c r="D130" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3928,7 +3881,7 @@
       <c r="C131" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="D131" s="6" t="s">
+      <c r="D131" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3942,7 +3895,7 @@
       <c r="C132" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D132" s="6" t="s">
+      <c r="D132" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3956,7 +3909,7 @@
       <c r="C133" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D133" s="6" t="s">
+      <c r="D133" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3970,7 +3923,7 @@
       <c r="C134" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D134" s="6" t="s">
+      <c r="D134" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3984,7 +3937,7 @@
       <c r="C135" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D135" s="6" t="s">
+      <c r="D135" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3998,7 +3951,7 @@
       <c r="C136" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D136" s="6" t="s">
+      <c r="D136" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4012,7 +3965,7 @@
       <c r="C137" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D137" s="6" t="s">
+      <c r="D137" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4026,7 +3979,7 @@
       <c r="C138" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D138" s="6" t="s">
+      <c r="D138" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4040,7 +3993,7 @@
       <c r="C139" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D139" s="6" t="s">
+      <c r="D139" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4054,7 +4007,7 @@
       <c r="C140" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D140" s="6" t="s">
+      <c r="D140" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4068,7 +4021,7 @@
       <c r="C141" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D141" s="6" t="s">
+      <c r="D141" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4082,7 +4035,7 @@
       <c r="C142" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D142" s="6" t="s">
+      <c r="D142" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4096,7 +4049,7 @@
       <c r="C143" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D143" s="6" t="s">
+      <c r="D143" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4110,7 +4063,7 @@
       <c r="C144" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D144" s="6" t="s">
+      <c r="D144" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4124,7 +4077,7 @@
       <c r="C145" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="D145" s="6" t="s">
+      <c r="D145" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4138,7 +4091,7 @@
       <c r="C146" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D146" s="6" t="s">
+      <c r="D146" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4152,7 +4105,7 @@
       <c r="C147" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D147" s="6" t="s">
+      <c r="D147" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4164,7 +4117,7 @@
       <c r="C148" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D148" s="6" t="s">
+      <c r="D148" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4176,7 +4129,7 @@
       <c r="C149" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D149" s="6" t="s">
+      <c r="D149" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4188,7 +4141,7 @@
       <c r="C150" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D150" s="6" t="s">
+      <c r="D150" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4200,7 +4153,7 @@
       <c r="C151" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D151" s="6" t="s">
+      <c r="D151" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4212,7 +4165,7 @@
       <c r="C152" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D152" s="6" t="s">
+      <c r="D152" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4224,7 +4177,7 @@
       <c r="C153" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D153" s="6" t="s">
+      <c r="D153" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4236,7 +4189,7 @@
       <c r="C154" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D154" s="6" t="s">
+      <c r="D154" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4248,7 +4201,7 @@
       <c r="C155" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D155" s="6" t="s">
+      <c r="D155" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4260,7 +4213,7 @@
       <c r="C156" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D156" s="6" t="s">
+      <c r="D156" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4272,7 +4225,7 @@
       <c r="C157" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D157" s="6" t="s">
+      <c r="D157" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4286,7 +4239,7 @@
       <c r="C158" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D158" s="6" t="s">
+      <c r="D158" s="2" t="s">
         <v>325</v>
       </c>
     </row>
@@ -4300,7 +4253,7 @@
       <c r="C159" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D159" s="6" t="s">
+      <c r="D159" s="2" t="s">
         <v>325</v>
       </c>
     </row>
@@ -4314,7 +4267,7 @@
       <c r="C160" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D160" s="6" t="s">
+      <c r="D160" s="2" t="s">
         <v>325</v>
       </c>
     </row>
@@ -4328,19 +4281,33 @@
       <c r="C161" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D161" s="6" t="s">
+      <c r="D161" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="31.5" x14ac:dyDescent="0.15">
+      <c r="A162" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D162" s="2" t="s">
         <v>325</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C148 C150:C1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C149">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
